--- a/publication_tables/main/table1.xlsx
+++ b/publication_tables/main/table1.xlsx
@@ -550,102 +550,78 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Variable</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Table 1. Benchmark household quintiles and resource shares</t>
+          <t>Description</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Quintile</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Note. Quintiles use person-weighted equivalised disposable income. Income and consumption shares use household expansion weights. Source: calculations from the 2024 HBS.</t>
+          <t>Income quintile ranked by baseline person-weighted equivalent income. Values follow the displayed precision of Table 1. Benchmark household quintiles and resource shares. Full-precision simulation results accompany the analysis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Sample households</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Number of sampled households in this quintile. Values follow the displayed precision of Table 1. Benchmark household quintiles and resource shares. Full-precision simulation results accompany the analysis.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Variable</t>
+          <t>Population (%)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Share of represented persons, percent. Values follow the displayed precision of Table 1. Benchmark household quintiles and resource shares. Full-precision simulation results accompany the analysis.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Quintile</t>
+          <t>Income (%)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Person-weighted benchmark income quintile, held fixed across simulations.</t>
+          <t>Share of baseline disposable income, percent. Values follow the displayed precision of Table 1. Benchmark household quintiles and resource shares. Full-precision simulation results accompany the analysis.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sample households</t>
+          <t>Consumption (%)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Unweighted number of HBS sample households assigned to the quintile.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Population (%)</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Share of represented persons in the quintile (%).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Income (%)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Share of disposable income using household expansion weights (%).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Consumption (%)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Share of consumption using household expansion weights (%).</t>
+          <t>Share of baseline consumption expenditure, percent. Values follow the displayed precision of Table 1. Benchmark household quintiles and resource shares. Full-precision simulation results accompany the analysis.</t>
         </is>
       </c>
     </row>
